--- a/output/graficos_dimensiones/comunal_d_env_a_2018_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_los lagos.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:14</t>
+    <t xml:space="preserve">2026-09-10 01:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_los lagos.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:28</t>
+    <t xml:space="preserve">2026-09-12 22:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_los lagos.xlsx
@@ -66,18 +66,18 @@
     <t xml:space="preserve">Quemchi</t>
   </si>
   <si>
+    <t xml:space="preserve">Palena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curaco de Vélez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quinchao</t>
+  </si>
+  <si>
     <t xml:space="preserve">Los Muermos</t>
   </si>
   <si>
-    <t xml:space="preserve">Quinchao</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curaco de Vélez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palena</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ancud</t>
   </si>
   <si>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:40</t>
+    <t xml:space="preserve">2026-09-24 00:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -568,7 +568,7 @@
         <v>2018</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>143.51</v>
+        <v>156.85</v>
       </c>
     </row>
     <row r="3">
@@ -585,7 +585,7 @@
         <v>2018</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>140.99</v>
+        <v>151.99</v>
       </c>
     </row>
     <row r="4">
@@ -602,7 +602,7 @@
         <v>2018</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>129.16</v>
+        <v>138.63</v>
       </c>
     </row>
     <row r="5">
@@ -619,7 +619,7 @@
         <v>2018</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>126.84</v>
+        <v>136.7</v>
       </c>
     </row>
     <row r="6">
@@ -636,7 +636,7 @@
         <v>2018</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>125.12</v>
+        <v>135.47</v>
       </c>
     </row>
     <row r="7">
@@ -653,7 +653,7 @@
         <v>2018</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>116.5</v>
+        <v>126.03</v>
       </c>
     </row>
     <row r="8">
@@ -670,7 +670,7 @@
         <v>2018</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>113.18</v>
+        <v>121.72</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         <v>2018</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>111.1</v>
+        <v>120.84</v>
       </c>
     </row>
     <row r="10">
@@ -704,7 +704,7 @@
         <v>2018</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>107.85</v>
+        <v>115.57</v>
       </c>
     </row>
     <row r="11">
@@ -721,7 +721,7 @@
         <v>2018</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>105.75</v>
+        <v>115.06</v>
       </c>
     </row>
     <row r="12">
@@ -732,13 +732,13 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>10106</v>
+        <v>10404</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>104.73</v>
+        <v>112.95</v>
       </c>
     </row>
     <row r="13">
@@ -749,13 +749,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>10210</v>
+        <v>10204</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>103.01</v>
+        <v>112.93</v>
       </c>
     </row>
     <row r="14">
@@ -766,13 +766,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>10204</v>
+        <v>10210</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>102.98</v>
+        <v>112.91</v>
       </c>
     </row>
     <row r="15">
@@ -783,13 +783,13 @@
         <v>19</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>10404</v>
+        <v>10106</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>102.35</v>
+        <v>112.43</v>
       </c>
     </row>
     <row r="16">
@@ -806,7 +806,7 @@
         <v>2018</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>96.23</v>
+        <v>104.16</v>
       </c>
     </row>
     <row r="17">
@@ -823,7 +823,7 @@
         <v>2018</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>93.6</v>
+        <v>101.58</v>
       </c>
     </row>
     <row r="18">
@@ -840,7 +840,7 @@
         <v>2018</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>92.03</v>
+        <v>100.68</v>
       </c>
     </row>
     <row r="19">
@@ -857,7 +857,7 @@
         <v>2018</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>91.51</v>
+        <v>97.3</v>
       </c>
     </row>
     <row r="20">
@@ -874,7 +874,7 @@
         <v>2018</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>87.41</v>
+        <v>94.79</v>
       </c>
     </row>
     <row r="21">
@@ -891,7 +891,7 @@
         <v>2018</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>86.12</v>
+        <v>93.23</v>
       </c>
     </row>
     <row r="22">
@@ -908,7 +908,7 @@
         <v>2018</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>84.73</v>
+        <v>91.86</v>
       </c>
     </row>
     <row r="23">
@@ -925,7 +925,7 @@
         <v>2018</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>83.75</v>
+        <v>89.75</v>
       </c>
     </row>
     <row r="24">
@@ -942,7 +942,7 @@
         <v>2018</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>83.3</v>
+        <v>85.74</v>
       </c>
     </row>
     <row r="25">
@@ -959,7 +959,7 @@
         <v>2018</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>78.46</v>
+        <v>83.64</v>
       </c>
     </row>
     <row r="26">
@@ -976,7 +976,7 @@
         <v>2018</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>72.25</v>
+        <v>78.41</v>
       </c>
     </row>
     <row r="27">
@@ -993,7 +993,7 @@
         <v>2018</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>71.03</v>
+        <v>76.28</v>
       </c>
     </row>
     <row r="28">
@@ -1010,7 +1010,7 @@
         <v>2018</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>69.13</v>
+        <v>74.73</v>
       </c>
     </row>
     <row r="29">
@@ -1027,7 +1027,7 @@
         <v>2018</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>66.12</v>
+        <v>70.88</v>
       </c>
     </row>
     <row r="30">
@@ -1044,7 +1044,7 @@
         <v>2018</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>56.71</v>
+        <v>60.84</v>
       </c>
     </row>
     <row r="31">
@@ -1061,7 +1061,7 @@
         <v>2018</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>49.45</v>
+        <v>52.79</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_los lagos.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:08</t>
+    <t xml:space="preserve">2026-10-02 15:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_los lagos.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:41</t>
+    <t xml:space="preserve">2026-10-05 16:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
